--- a/supplementary-materials/tables/Table_S14.xlsx
+++ b/supplementary-materials/tables/Table_S14.xlsx
@@ -149,7 +149,7 @@
     <t>Excludes centroid-outside-city and categorical permanent-water cells</t>
   </si>
   <si>
-    <t>Planning-facing city summaries in S7-S8</t>
+    <t/>
   </si>
   <si>
     <t>Note. The H4 AOA uses only static environmental variables. One AOA and one combined-tier label therefore accompany all 52 annual weeks; no week-specific, majority or worst-week aggregation is used.</t>
@@ -188,7 +188,7 @@
     <t>Centroid-in-city Primary Results + Moderate Extrapolation</t>
   </si>
   <si>
-    <t>Excludes Monitoring Gaps and Outside the Reporting Domain</t>
+    <t/>
   </si>
 </sst>
 </file>
